--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -2243,43 +2243,43 @@
         </is>
       </c>
       <c r="E75" s="16">
-        <f>MAX(0,E68-E74-E84)</f>
+        <f>MAX(0,E68-E74-E85)</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>MAX(0,F68-F74-F84)</f>
+        <f>MAX(0,F68-F74-F85)</f>
         <v/>
       </c>
       <c r="G75" s="16">
-        <f>MAX(0,G68-G74-G84)</f>
+        <f>MAX(0,G68-G74-G85)</f>
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>MAX(0,H68-H74-H84)</f>
+        <f>MAX(0,H68-H74-H85)</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>MAX(0,I68-I74-I84)</f>
+        <f>MAX(0,I68-I74-I85)</f>
         <v/>
       </c>
       <c r="J75" s="16">
-        <f>MAX(0,J68-J74-J84)</f>
+        <f>MAX(0,J68-J74-J85)</f>
         <v/>
       </c>
       <c r="K75" s="16">
-        <f>MAX(0,K68-K74-K84)</f>
+        <f>MAX(0,K68-K74-K85)</f>
         <v/>
       </c>
       <c r="L75" s="16">
-        <f>MAX(0,L68-L74-L84)</f>
+        <f>MAX(0,L68-L74-L85)</f>
         <v/>
       </c>
       <c r="M75" s="16">
-        <f>MAX(0,M68-M74-M84)</f>
+        <f>MAX(0,M68-M74-M85)</f>
         <v/>
       </c>
       <c r="N75" s="16">
-        <f>MAX(0,N68-N74-N84)</f>
+        <f>MAX(0,N68-N74-N85)</f>
         <v/>
       </c>
     </row>
@@ -2511,91 +2511,87 @@
         <v/>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled DS (for DSRA)</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Based on straight-line amort, no sweep</t>
+        </is>
+      </c>
+      <c r="E80" s="16">
+        <f>MAX(0,$D$50-(1-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="F80" s="16">
+        <f>MAX(0,$D$50-(2-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="G80" s="16">
+        <f>MAX(0,$D$50-(3-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="H80" s="16">
+        <f>MAX(0,$D$50-(4-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="I80" s="16">
+        <f>MAX(0,$D$50-(5-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="J80" s="16">
+        <f>MAX(0,$D$50-(6-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="K80" s="16">
+        <f>MAX(0,$D$50-(7-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="L80" s="16">
+        <f>MAX(0,$D$50-(8-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="M80" s="16">
+        <f>MAX(0,$D$50-(9-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="N80" s="16">
+        <f>MAX(0,$D$50-(10-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>DSRA (Debt Service Reserve Account)</t>
         </is>
       </c>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Target</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D82" s="16">
-        <f>E74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="E82" s="16">
-        <f>F74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="F82" s="16">
-        <f>G74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="G82" s="16">
-        <f>H74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="H82" s="16">
-        <f>I74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="I82" s="16">
-        <f>J74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="J82" s="16">
-        <f>K74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="K82" s="16">
-        <f>L74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="L82" s="16">
-        <f>M74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="M82" s="16">
-        <f>N74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="N82" s="16">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Target</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2603,56 +2599,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr"/>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
       <c r="D83" s="16">
+        <f>E80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="E83" s="16">
+        <f>F80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="F83" s="16">
+        <f>G80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="G83" s="16">
+        <f>H80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="H83" s="16">
+        <f>I80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="I83" s="16">
+        <f>J80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="J83" s="16">
+        <f>K80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="K83" s="16">
+        <f>L80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="L83" s="16">
+        <f>M80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="M83" s="16">
+        <f>N80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="N83" s="16">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="E83" s="16">
-        <f>D85</f>
-        <v/>
-      </c>
-      <c r="F83" s="16">
-        <f>E85</f>
-        <v/>
-      </c>
-      <c r="G83" s="16">
-        <f>F85</f>
-        <v/>
-      </c>
-      <c r="H83" s="16">
-        <f>G85</f>
-        <v/>
-      </c>
-      <c r="I83" s="16">
-        <f>H85</f>
-        <v/>
-      </c>
-      <c r="J83" s="16">
-        <f>I85</f>
-        <v/>
-      </c>
-      <c r="K83" s="16">
-        <f>J85</f>
-        <v/>
-      </c>
-      <c r="L83" s="16">
-        <f>K85</f>
-        <v/>
-      </c>
-      <c r="M83" s="16">
-        <f>L85</f>
-        <v/>
-      </c>
-      <c r="N83" s="16">
-        <f>M85</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -2660,114 +2660,171 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Target - Beginning</t>
-        </is>
-      </c>
+      <c r="C84" s="6" t="inlineStr"/>
       <c r="D84" s="16">
-        <f>D82-D83</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E84" s="16">
-        <f>E82-E83</f>
+        <f>D86</f>
         <v/>
       </c>
       <c r="F84" s="16">
-        <f>F82-F83</f>
+        <f>E86</f>
         <v/>
       </c>
       <c r="G84" s="16">
-        <f>G82-G83</f>
+        <f>F86</f>
         <v/>
       </c>
       <c r="H84" s="16">
-        <f>H82-H83</f>
+        <f>G86</f>
         <v/>
       </c>
       <c r="I84" s="16">
-        <f>I82-I83</f>
+        <f>H86</f>
         <v/>
       </c>
       <c r="J84" s="16">
-        <f>J82-J83</f>
+        <f>I86</f>
         <v/>
       </c>
       <c r="K84" s="16">
-        <f>K82-K83</f>
+        <f>J86</f>
         <v/>
       </c>
       <c r="L84" s="16">
-        <f>L82-L83</f>
+        <f>K86</f>
         <v/>
       </c>
       <c r="M84" s="16">
-        <f>M82-M83</f>
+        <f>L86</f>
         <v/>
       </c>
       <c r="N84" s="16">
-        <f>N82-N83</f>
+        <f>M86</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>DSRA Funding/(Release)</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D85" s="16">
+        <f>D83-D84</f>
+        <v/>
+      </c>
+      <c r="E85" s="16">
+        <f>E83-E84</f>
+        <v/>
+      </c>
+      <c r="F85" s="16">
+        <f>F83-F84</f>
+        <v/>
+      </c>
+      <c r="G85" s="16">
+        <f>G83-G84</f>
+        <v/>
+      </c>
+      <c r="H85" s="16">
+        <f>H83-H84</f>
+        <v/>
+      </c>
+      <c r="I85" s="16">
+        <f>I83-I84</f>
+        <v/>
+      </c>
+      <c r="J85" s="16">
+        <f>J83-J84</f>
+        <v/>
+      </c>
+      <c r="K85" s="16">
+        <f>K83-K84</f>
+        <v/>
+      </c>
+      <c r="L85" s="16">
+        <f>L83-L84</f>
+        <v/>
+      </c>
+      <c r="M85" s="16">
+        <f>M83-M84</f>
+        <v/>
+      </c>
+      <c r="N85" s="16">
+        <f>N83-N84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
           <t>DSRA Ending</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>Beginning + Funding</t>
         </is>
       </c>
-      <c r="D85" s="16">
-        <f>D83+D84</f>
-        <v/>
-      </c>
-      <c r="E85" s="16">
-        <f>E83+E84</f>
-        <v/>
-      </c>
-      <c r="F85" s="16">
-        <f>F83+F84</f>
-        <v/>
-      </c>
-      <c r="G85" s="16">
-        <f>G83+G84</f>
-        <v/>
-      </c>
-      <c r="H85" s="16">
-        <f>H83+H84</f>
-        <v/>
-      </c>
-      <c r="I85" s="16">
-        <f>I83+I84</f>
-        <v/>
-      </c>
-      <c r="J85" s="16">
-        <f>J83+J84</f>
-        <v/>
-      </c>
-      <c r="K85" s="16">
-        <f>K83+K84</f>
-        <v/>
-      </c>
-      <c r="L85" s="16">
-        <f>L83+L84</f>
-        <v/>
-      </c>
-      <c r="M85" s="16">
-        <f>M83+M84</f>
-        <v/>
-      </c>
-      <c r="N85" s="16">
-        <f>N83+N84</f>
+      <c r="D86" s="16">
+        <f>D84+D85</f>
+        <v/>
+      </c>
+      <c r="E86" s="16">
+        <f>E84+E85</f>
+        <v/>
+      </c>
+      <c r="F86" s="16">
+        <f>F84+F85</f>
+        <v/>
+      </c>
+      <c r="G86" s="16">
+        <f>G84+G85</f>
+        <v/>
+      </c>
+      <c r="H86" s="16">
+        <f>H84+H85</f>
+        <v/>
+      </c>
+      <c r="I86" s="16">
+        <f>I84+I85</f>
+        <v/>
+      </c>
+      <c r="J86" s="16">
+        <f>J84+J85</f>
+        <v/>
+      </c>
+      <c r="K86" s="16">
+        <f>K84+K85</f>
+        <v/>
+      </c>
+      <c r="L86" s="16">
+        <f>L84+L85</f>
+        <v/>
+      </c>
+      <c r="M86" s="16">
+        <f>M84+M85</f>
+        <v/>
+      </c>
+      <c r="N86" s="16">
+        <f>N84+N85</f>
         <v/>
       </c>
     </row>
@@ -2808,43 +2865,43 @@
         </is>
       </c>
       <c r="E88" s="16">
-        <f>E68-(E72+E77)-E84</f>
+        <f>E68-(E72+E77)-E85</f>
         <v/>
       </c>
       <c r="F88" s="16">
-        <f>F68-(F72+F77)-F84</f>
+        <f>F68-(F72+F77)-F85</f>
         <v/>
       </c>
       <c r="G88" s="16">
-        <f>G68-(G72+G77)-G84</f>
+        <f>G68-(G72+G77)-G85</f>
         <v/>
       </c>
       <c r="H88" s="16">
-        <f>H68-(H72+H77)-H84</f>
+        <f>H68-(H72+H77)-H85</f>
         <v/>
       </c>
       <c r="I88" s="16">
-        <f>I68-(I72+I77)-I84</f>
+        <f>I68-(I72+I77)-I85</f>
         <v/>
       </c>
       <c r="J88" s="16">
-        <f>J68-(J72+J77)-J84</f>
+        <f>J68-(J72+J77)-J85</f>
         <v/>
       </c>
       <c r="K88" s="16">
-        <f>K68-(K72+K77)-K84</f>
+        <f>K68-(K72+K77)-K85</f>
         <v/>
       </c>
       <c r="L88" s="16">
-        <f>L68-(L72+L77)-L84</f>
+        <f>L68-(L72+L77)-L85</f>
         <v/>
       </c>
       <c r="M88" s="16">
-        <f>M68-(M72+M77)-M84</f>
+        <f>M68-(M72+M77)-M85</f>
         <v/>
       </c>
       <c r="N88" s="16">
-        <f>N68-(N72+N77)-N84</f>
+        <f>N68-(N72+N77)-N85</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3091,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr"/>
       <c r="D96" s="16">
-        <f>D82</f>
+        <f>D83</f>
         <v/>
       </c>
     </row>
@@ -3211,7 +3268,7 @@
         </is>
       </c>
       <c r="K108" s="16">
-        <f>K85</f>
+        <f>K86</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,11 +19,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0_);(#,##0.0)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,21 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -117,12 +133,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,6 +147,14 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -205,6 +229,246 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0">
+      <text>
+        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
+      <text>
+        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="0" shapeId="0">
+      <text>
+        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="0" shapeId="0">
+      <text>
+        <t>Volume growth as new wells come online. Typical growth phase Y1-5 as basin develops.</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0">
+      <text>
+        <t>Volume decline as reservoir depletes. 5%/yr typical for mature basin. Accelerates in late life.</t>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0" shapeId="0">
+      <text>
+        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0">
+      <text>
+        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="0" shapeId="0">
+      <text>
+        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0" shapeId="0">
+      <text>
+        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="0" shapeId="0">
+      <text>
+        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="0" shapeId="0">
+      <text>
+        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0">
+      <text>
+        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0" shapeId="0">
+      <text>
+        <t>Excludes land (~15% of EV). Depreciation creates tax shield, improves after-tax cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="C55" authorId="0" shapeId="0">
+      <text>
+        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
+      </text>
+    </comment>
+    <comment ref="C56" authorId="0" shapeId="0">
+      <text>
+        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
+      </text>
+    </comment>
+    <comment ref="C57" authorId="0" shapeId="0">
+      <text>
+        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
+      </text>
+    </comment>
+    <comment ref="C62" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C68" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C70" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C71" authorId="0" shapeId="0">
+      <text>
+        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
+      </text>
+    </comment>
+    <comment ref="C72" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C74" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C76" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C78" authorId="0" shapeId="0">
+      <text>
+        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+      </text>
+    </comment>
+    <comment ref="C79" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C83" authorId="0" shapeId="0">
+      <text>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
+      </text>
+    </comment>
+    <comment ref="C85" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C90" authorId="0" shapeId="0">
+      <text>
+        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
+      </text>
+    </comment>
+    <comment ref="C95" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C96" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C113" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C114" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C118" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -586,7 +850,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
       <c r="D3" s="7">
         <f>$D$17</f>
         <v/>
@@ -603,7 +871,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="D4" s="7">
         <f>E62</f>
         <v/>
@@ -620,7 +891,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
+      <c r="C5" s="6">
+        <f> EBITDA − Taxes</f>
+        <v/>
+      </c>
       <c r="D5" s="7">
         <f>AVERAGE(E68:I68)</f>
         <v/>
@@ -637,8 +911,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="8">
+      <c r="C6" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
+      <c r="D6" s="22">
         <f>MIN(E79:I79)</f>
         <v/>
       </c>
@@ -654,8 +931,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="9">
+      <c r="C7" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D7" s="23">
         <f>D113</f>
         <v/>
       </c>
@@ -671,8 +951,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="8">
+      <c r="C8" s="6">
+        <f> Total In / Total Out</f>
+        <v/>
+      </c>
+      <c r="D8" s="22">
         <f>D114</f>
         <v/>
       </c>
@@ -688,8 +971,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D9" s="23">
         <f>D118</f>
         <v/>
       </c>
@@ -747,7 +1033,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
@@ -809,7 +1098,7 @@
           <t>Legal, advisory, financing</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="24" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -829,7 +1118,7 @@
           <t>Compressed for decline</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="25" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -860,7 +1149,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
+      <c r="C22" s="4">
+        <f> Growth then Decline</f>
+        <v/>
+      </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
@@ -909,7 +1201,7 @@
           <t>Drilling phase</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D24" s="24" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -929,7 +1221,7 @@
           <t>Depletion phase</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="24" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -989,7 +1281,7 @@
           <t>Contract escalation</t>
         </is>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -1049,7 +1341,7 @@
           <t>Cost escalation</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="24" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1109,7 +1401,7 @@
           <t>Debt / Entry EV</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D37" s="24" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1129,7 +1421,7 @@
           <t>Higher (basin risk)</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="24" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -1189,7 +1481,7 @@
           <t>Aggressive paydown</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D41" s="24" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1209,7 +1501,7 @@
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="25" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1249,7 +1541,7 @@
           <t>Blended federal + state</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="D45" s="24" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1269,7 +1561,7 @@
           <t>% of EV for depreciation</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="24" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1523,7 +1815,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Escalated</t>
+          <t>$/Mcf gathering fee</t>
         </is>
       </c>
       <c r="E57" s="18">
@@ -1692,7 +1984,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr"/>
+      <c r="C62" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="E62" s="7">
         <f>E59-E60</f>
         <v/>
@@ -1989,7 +2284,11 @@
         </is>
       </c>
       <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
@@ -2013,7 +2312,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr"/>
+      <c r="C71" s="6">
+        <f> Prior Yr End Bal</f>
+        <v/>
+      </c>
       <c r="E71" s="16">
         <f>$D$50</f>
         <v/>
@@ -2470,43 +2772,43 @@
           <t>CFADS / Debt Service</t>
         </is>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="22">
         <f>IF(E74&gt;0,E68/E74,0)</f>
         <v/>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="22">
         <f>IF(F74&gt;0,F68/F74,0)</f>
         <v/>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="22">
         <f>IF(G74&gt;0,G68/G74,0)</f>
         <v/>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="22">
         <f>IF(H74&gt;0,H68/H74,0)</f>
         <v/>
       </c>
-      <c r="I79" s="8">
+      <c r="I79" s="22">
         <f>IF(I74&gt;0,I68/I74,0)</f>
         <v/>
       </c>
-      <c r="J79" s="8">
+      <c r="J79" s="22">
         <f>IF(J74&gt;0,J68/J74,0)</f>
         <v/>
       </c>
-      <c r="K79" s="8">
+      <c r="K79" s="22">
         <f>IF(K74&gt;0,K68/K74,0)</f>
         <v/>
       </c>
-      <c r="L79" s="8">
+      <c r="L79" s="22">
         <f>IF(L74&gt;0,L68/L74,0)</f>
         <v/>
       </c>
-      <c r="M79" s="8">
+      <c r="M79" s="22">
         <f>IF(M74&gt;0,M68/M74,0)</f>
         <v/>
       </c>
-      <c r="N79" s="8">
+      <c r="N79" s="22">
         <f>IF(N74&gt;0,N68/N74,0)</f>
         <v/>
       </c>
@@ -3072,7 +3374,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr"/>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>% of EV for legal, advisory</t>
+        </is>
+      </c>
       <c r="D95" s="16">
         <f>$D$17*$D$18</f>
         <v/>
@@ -3089,7 +3395,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr"/>
+      <c r="C96" s="6">
+        <f> Target − Beginning</f>
+        <v/>
+      </c>
       <c r="D96" s="16">
         <f>D83</f>
         <v/>
@@ -3381,8 +3690,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr"/>
-      <c r="D113" s="9">
+      <c r="C113" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D113" s="23">
         <f>IRR(D112:K112)</f>
         <v/>
       </c>
@@ -3403,7 +3715,7 @@
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="22">
         <f>SUMIF(D112:K112,"&gt;0")/ABS(D112)</f>
         <v/>
       </c>
@@ -3485,10 +3797,204 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr"/>
-      <c r="D118" s="9">
+      <c r="C118" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D118" s="23">
         <f>IRR(D117:K117)</f>
         <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Natural Gas Gathering System</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>• Acquire gas gathering system at $85mm (6.5x EBITDA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>• Fee-based revenue with minimum volume commitments</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>• Growth phase Y1-5 (3%/yr), decline Y6+ (5%/yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>• Target returns: 16-18% levered IRR, 2.2-2.5x MOIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>1. Fee-based, volume-protected revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   MVCs provide downside protection. Fee structure insulates from commodity prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>2. Near-term growth optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Undeveloped acreage dedication provides volume upside as producer drills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>3. Aggressive deleveraging</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   75% cash sweep with 5-year tenor rapidly pays down debt before decline phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Risk | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Producer credit risk | Investment-grade anchor shipper; diversified producer base</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Volume decline steeper than modeled | Conservative decline assumptions; exit before steep decline</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Commodity price impact on drilling | MVC protection; acreage dedication locks in volumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>FINANCIAL SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Entry EV: $85mm | Leverage: 55% | Min DSCR: 1.35x</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Levered IRR: 17.0% | MOIC: 2.3x</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,21 +52,6 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -120,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,10 +135,6 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -239,232 +219,102 @@
   <commentList>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C13" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C17" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0" shapeId="0">
-      <text>
-        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
-      </text>
-    </comment>
-    <comment ref="C22" authorId="0" shapeId="0">
-      <text>
-        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
-      </text>
-    </comment>
-    <comment ref="C23" authorId="0" shapeId="0">
-      <text>
-        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
-      </text>
-    </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
-      <text>
-        <t>Volume growth as new wells come online. Typical growth phase Y1-5 as basin develops.</t>
-      </text>
-    </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
-      <text>
-        <t>Volume decline as reservoir depletes. 5%/yr typical for mature basin. Accelerates in late life.</t>
-      </text>
-    </comment>
-    <comment ref="C28" authorId="0" shapeId="0">
-      <text>
-        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
-      </text>
-    </comment>
-    <comment ref="C29" authorId="0" shapeId="0">
-      <text>
-        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
-      </text>
-    </comment>
-    <comment ref="C37" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
-      </text>
-    </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
-      <text>
-        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
-      </text>
-    </comment>
-    <comment ref="C39" authorId="0" shapeId="0">
-      <text>
-        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
-      </text>
-    </comment>
-    <comment ref="C40" authorId="0" shapeId="0">
-      <text>
-        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C41" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C42" authorId="0" shapeId="0">
       <text>
-        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
-      </text>
-    </comment>
-    <comment ref="C45" authorId="0" shapeId="0">
-      <text>
-        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
-      </text>
-    </comment>
-    <comment ref="C46" authorId="0" shapeId="0">
-      <text>
-        <t>Excludes land (~15% of EV). Depreciation creates tax shield, improves after-tax cash flow.</t>
-      </text>
-    </comment>
-    <comment ref="C55" authorId="0" shapeId="0">
-      <text>
-        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
-      </text>
-    </comment>
-    <comment ref="C56" authorId="0" shapeId="0">
-      <text>
-        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
-      </text>
-    </comment>
-    <comment ref="C57" authorId="0" shapeId="0">
-      <text>
-        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C62" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C68" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
-      </text>
-    </comment>
-    <comment ref="C70" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C71" authorId="0" shapeId="0">
-      <text>
-        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
-      </text>
-    </comment>
-    <comment ref="C72" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C74" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C76" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C78" authorId="0" shapeId="0">
-      <text>
-        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C79" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C80" authorId="0" shapeId="0">
+      <text>
+        <t>Debt service using straight-line principal only. Used for DSRA to avoid circularity.</t>
       </text>
     </comment>
     <comment ref="C83" authorId="0" shapeId="0">
       <text>
-        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
-      </text>
-    </comment>
-    <comment ref="C85" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
-      </text>
-    </comment>
-    <comment ref="C90" authorId="0" shapeId="0">
-      <text>
-        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
-      </text>
-    </comment>
-    <comment ref="C95" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C96" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS to avoid circular reference.</t>
       </text>
     </comment>
     <comment ref="C113" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C114" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C118" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
   </commentList>
@@ -760,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -871,9 +721,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="D4" s="7">
         <f>E62</f>
@@ -891,9 +742,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6">
-        <f> EBITDA − Taxes</f>
-        <v/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA minus Taxes</t>
+        </is>
       </c>
       <c r="D5" s="7">
         <f>AVERAGE(E68:I68)</f>
@@ -911,9 +763,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D6" s="22">
         <f>MIN(E79:I79)</f>
@@ -931,9 +784,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D7" s="23">
         <f>D113</f>
@@ -951,9 +805,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6">
-        <f> Total In / Total Out</f>
-        <v/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Total In / Total Out</t>
+        </is>
       </c>
       <c r="D8" s="22">
         <f>D114</f>
@@ -971,9 +826,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D9" s="23">
         <f>D118</f>
@@ -1033,15 +889,18 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1142,6 +1001,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1149,10 +1009,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4">
-        <f> Growth then Decline</f>
-        <v/>
-      </c>
+      <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
@@ -1225,6 +1082,7 @@
         <v>0.05</v>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1285,6 +1143,7 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -1365,6 +1224,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -1505,6 +1365,7 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -1585,6 +1446,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -1668,6 +1530,7 @@
         <v/>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -1815,7 +1678,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>$/Mcf gathering fee</t>
+          <t>Escalated</t>
         </is>
       </c>
       <c r="E57" s="18">
@@ -1859,6 +1722,7 @@
         <v/>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
@@ -1973,6 +1837,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
@@ -1984,9 +1849,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C62" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="E62" s="7">
         <f>E59-E60</f>
@@ -2029,6 +1895,7 @@
         <v/>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -2277,6 +2144,7 @@
         <v/>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
@@ -2284,11 +2152,7 @@
         </is>
       </c>
       <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>% of excess cash to prepay</t>
-        </is>
-      </c>
+      <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
@@ -2312,10 +2176,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C71" s="6">
-        <f> Prior Yr End Bal</f>
-        <v/>
-      </c>
+      <c r="C71" s="6" t="inlineStr"/>
       <c r="E71" s="16">
         <f>$D$50</f>
         <v/>
@@ -2870,6 +2731,7 @@
         <v/>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
@@ -3317,6 +3179,7 @@
         <v/>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -3374,11 +3237,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>% of EV for legal, advisory</t>
-        </is>
-      </c>
+      <c r="C95" s="6" t="inlineStr"/>
       <c r="D95" s="16">
         <f>$D$17*$D$18</f>
         <v/>
@@ -3395,10 +3254,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C96" s="6">
-        <f> Target − Beginning</f>
-        <v/>
-      </c>
+      <c r="C96" s="6" t="inlineStr"/>
       <c r="D96" s="16">
         <f>D83</f>
         <v/>
@@ -3421,6 +3277,7 @@
         <v/>
       </c>
     </row>
+    <row r="98"/>
     <row r="99">
       <c r="A99" s="21" t="inlineStr">
         <is>
@@ -3498,6 +3355,7 @@
         <v/>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -3602,6 +3460,7 @@
         <v/>
       </c>
     </row>
+    <row r="110"/>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
@@ -3690,9 +3549,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C113" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D113" s="23">
         <f>IRR(D112:K112)</f>
@@ -3720,6 +3580,7 @@
         <v/>
       </c>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
         <is>
@@ -3797,207 +3658,59 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C118" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D118" s="23">
         <f>IRR(D117:K117)</f>
         <v/>
       </c>
     </row>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Natural Gas Gathering System</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>EXECUTIVE SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>• Acquire gas gathering system at $85mm (6.5x EBITDA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>• Fee-based revenue with minimum volume commitments</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>• Growth phase Y1-5 (3%/yr), decline Y6+ (5%/yr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>• Target returns: 16-18% levered IRR, 2.2-2.5x MOIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>1. Fee-based, volume-protected revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   MVCs provide downside protection. Fee structure insulates from commodity prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>2. Near-term growth optionality</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Undeveloped acreage dedication provides volume upside as producer drills.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>3. Aggressive deleveraging</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   75% cash sweep with 5-year tenor rapidly pays down debt before decline phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>Risk | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Producer credit risk | Investment-grade anchor shipper; diversified producer base</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>Volume decline steeper than modeled | Conservative decline assumptions; exit before steep decline</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>Commodity price impact on drilling | MVC protection; acreage dedication locks in volumes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>FINANCIAL SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Entry EV: $85mm | Leverage: 55% | Min DSCR: 1.35x</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>Levered IRR: 17.0% | MOIC: 2.3x</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,20 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -135,6 +150,15 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -610,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -899,8 +923,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1001,7 +1023,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1082,7 +1103,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1143,7 +1163,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -1224,7 +1243,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -1365,7 +1383,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -1446,7 +1463,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -1530,7 +1546,6 @@
         <v/>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -1722,7 +1737,6 @@
         <v/>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
@@ -1837,7 +1851,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
@@ -1895,7 +1908,6 @@
         <v/>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -2144,7 +2156,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
@@ -2731,7 +2742,6 @@
         <v/>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
@@ -3179,7 +3189,6 @@
         <v/>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -3277,7 +3286,6 @@
         <v/>
       </c>
     </row>
-    <row r="98"/>
     <row r="99">
       <c r="A99" s="21" t="inlineStr">
         <is>
@@ -3355,7 +3363,6 @@
         <v/>
       </c>
     </row>
-    <row r="104"/>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -3460,7 +3467,6 @@
         <v/>
       </c>
     </row>
-    <row r="110"/>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
@@ -3580,7 +3586,6 @@
         <v/>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
         <is>
@@ -3668,49 +3673,262 @@
         <v/>
       </c>
     </row>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>PROJECT PERMIAN GATHERING</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>80 MMcf/d Gas Gathering System – Permian Basin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $85mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>• Fee-for-service model eliminates commodity price exposure – paid to move gas, not sell it</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>• Active drilling program supports 3%/year volume growth through Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>• Aggressive 75% sweep with 5-year tenor ensures debt payoff before decline phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>• Exit to producer seeking vertical integration or larger midstream for basin consolidation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Q: Why the growth-then-decline profile?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>A: Y1-Y5: Active drilling connects new wells (3%/year growth). Y6+: Drilling slows, existing wells deplete naturally (5%/year decline). Must structure debt to pay off before decline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Q: Why 5-year tenor vs 7 years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>A: Debt must be repaid during growth phase when CFADS is strong. Cannot service debt with declining cash flows. Short tenor + aggressive sweep = de-risked debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Q: What's the commodity exposure?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>A: Direct: None – fee-for-service. Indirect: Low gas prices → less drilling → lower volumes. Mitigated by acreage dedication and producer economics (breakeven $2.50/mmBtu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Q: Why compressed 6.5x exit multiple?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>A: Declining asset commands lower multiple than stable/growing. At exit (Y7), asset has 3-4 years of decline remaining. Buyer pricing reflects PDP-like valuation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Entry EV | $85mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 5.8x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Leverage | 30% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Levered IRR | 19.2% | 15.5% | 23.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>MOIC | 2.05x | 1.75x | 2.35x</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Min DSCR (Y1-Y5) | 1.65x | 1.45x | 1.85x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Producer curtails drilling | Medium | Acreage dedication provides volume floor; producer needs gatherer to monetize</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Volume decline steeper than forecast | Medium | 5%/year decline is conservative for Permian; exit at Y7 before steep decline</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>Single counterparty concentration | Medium | Producer is well-capitalized; consider credit support</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Basin differentials widen | Low | Fee-based, not commodity-based; producer bears basis risk</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +69,9 @@
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +164,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,6 +640,420 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Midstream - INTUITION MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>WHAT THIS MODEL DOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gas gathering - Fee revenue tied to basin production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>KEY VALUE DRIVERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1. Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2. Take-or-Pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3. Recontracting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>DEBT STRUCTURE RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>75% sweep - volume uncertainty.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: Midstream ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>500 MMcf/d gathering in Permian at $400mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>PROJECT PERMIAN GATHERING</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>80 MMcf/d Gas Gathering System – Permian Basin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $85mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>• Fee-for-service model eliminates commodity price exposure – paid to move gas, not sell it</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>• Active drilling program supports 3%/year volume growth through Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>• Aggressive 75% sweep with 5-year tenor ensures debt payoff before decline phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>• Exit to producer seeking vertical integration or larger midstream for basin consolidation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Q: Why the growth-then-decline profile?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>A: Y1-Y5: Active drilling connects new wells (3%/year growth). Y6+: Drilling slows, existing wells deplete naturally (5%/year decline). Must structure debt to pay off before decline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Q: Why 5-year tenor vs 7 years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>A: Debt must be repaid during growth phase when CFADS is strong. Cannot service debt with declining cash flows. Short tenor + aggressive sweep = de-risked debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Q: What's the commodity exposure?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>A: Direct: None – fee-for-service. Indirect: Low gas prices → less drilling → lower volumes. Mitigated by acreage dedication and producer economics (breakeven $2.50/mmBtu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Q: Why compressed 6.5x exit multiple?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>A: Declining asset commands lower multiple than stable/growing. At exit (Y7), asset has 3-4 years of decline remaining. Buyer pricing reflects PDP-like valuation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Entry EV | $85mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 5.8x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Leverage | 30% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Levered IRR | 19.2% | 15.5% | 23.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>MOIC | 2.05x | 1.75x | 2.35x</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Min DSCR (Y1-Y5) | 1.65x | 1.45x | 1.85x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Producer curtails drilling | Medium | Acreage dedication provides volume floor; producer needs gatherer to monetize</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Volume decline steeper than forecast | Medium | 5%/year decline is conservative for Permian; exit at Y7 before steep decline</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>Single counterparty concentration | Medium | Producer is well-capitalized; consider credit support</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Basin differentials widen | Low | Fee-based, not commodity-based; producer bears basis risk</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -793,7 +1213,7 @@
         </is>
       </c>
       <c r="D6" s="22">
-        <f>MIN(E79:I79)</f>
+        <f>IF(COUNTIF(E79:I79,"&gt;0")&gt;0,MINIFS(E79:I79,E79:I79,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -3677,258 +4097,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>PROJECT PERMIAN GATHERING</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>80 MMcf/d Gas Gathering System – Permian Basin</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION: Proceed to final bid at $85mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>KEY METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>• Fee-for-service model eliminates commodity price exposure – paid to move gas, not sell it</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>• Active drilling program supports 3%/year volume growth through Y5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>• Aggressive 75% sweep with 5-year tenor ensures debt payoff before decline phase</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>• Exit to producer seeking vertical integration or larger midstream for basin consolidation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>ANTICIPATED IC Q&amp;A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Q: Why the growth-then-decline profile?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>A: Y1-Y5: Active drilling connects new wells (3%/year growth). Y6+: Drilling slows, existing wells deplete naturally (5%/year decline). Must structure debt to pay off before decline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Q: Why 5-year tenor vs 7 years?</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>A: Debt must be repaid during growth phase when CFADS is strong. Cannot service debt with declining cash flows. Short tenor + aggressive sweep = de-risked debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Q: What's the commodity exposure?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>A: Direct: None – fee-for-service. Indirect: Low gas prices → less drilling → lower volumes. Mitigated by acreage dedication and producer economics (breakeven $2.50/mmBtu).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>Q: Why compressed 6.5x exit multiple?</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>A: Declining asset commands lower multiple than stable/growing. At exit (Y7), asset has 3-4 years of decline remaining. Buyer pricing reflects PDP-like valuation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Metric | Base Case | Downside | Upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>Entry EV | $85mm | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Entry Multiple | 5.8x Y1 EBITDA | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>Leverage | 30% | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>Levered IRR | 19.2% | 15.5% | 23.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>MOIC | 2.05x | 1.75x | 2.35x</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y5) | 1.65x | 1.45x | 1.85x</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>Risk | Probability | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>Producer curtails drilling | Medium | Acreage dedication provides volume floor; producer needs gatherer to monetize</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>Volume decline steeper than forecast | Medium | 5%/year decline is conservative for Permian; exit at Y7 before steep decline</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>Single counterparty concentration | Medium | Producer is well-capitalized; consider credit support</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>Basin differentials widen | Low | Fee-based, not commodity-based; producer bears basis risk</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -2157,6 +2157,7 @@
         <v/>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
@@ -2174,43 +2175,43 @@
         </is>
       </c>
       <c r="E59" s="16">
-        <f>E56*E57*1000</f>
+        <f>E56*E57</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>F56*F57*1000</f>
+        <f>F56*F57</f>
         <v/>
       </c>
       <c r="G59" s="16">
-        <f>G56*G57*1000</f>
+        <f>G56*G57</f>
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>H56*H57*1000</f>
+        <f>H56*H57</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>I56*I57*1000</f>
+        <f>I56*I57</f>
         <v/>
       </c>
       <c r="J59" s="16">
-        <f>J56*J57*1000</f>
+        <f>J56*J57</f>
         <v/>
       </c>
       <c r="K59" s="16">
-        <f>K56*K57*1000</f>
+        <f>K56*K57</f>
         <v/>
       </c>
       <c r="L59" s="16">
-        <f>L56*L57*1000</f>
+        <f>L56*L57</f>
         <v/>
       </c>
       <c r="M59" s="16">
-        <f>M56*M57*1000</f>
+        <f>M56*M57</f>
         <v/>
       </c>
       <c r="N59" s="16">
-        <f>N56*N57*1000</f>
+        <f>N56*N57</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
     </font>
   </fonts>
   <fills count="6">
@@ -124,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,6 +169,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,72 +651,648 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Midstream - INTUITION MAP</t>
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>WHAT THIS MODEL DOES</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: NATURAL GAS GATHERING SYSTEM ACQUISITION</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gas gathering - Fee revenue tied to basin production.</t>
-        </is>
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>KEY VALUE DRIVERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1. Volume</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2. Take-or-Pay</t>
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. Recontracting</t>
+          <t>Year 0 (2025): Transaction close Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1-5 (2026-2030): Growth phase; volumes increase with new connections</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>DEBT STRUCTURE RATIONALE</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 5 (2030): Anchor shipper contract expires; recontracting risk</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>75% sweep - volume uncertainty.</t>
+          <t>Year 6-10 (2031-2035): Potential decline phase if no new drilling</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating a natural gas gathering
+system in the Permian Basin (Delaware sub-basin). Nameplate capacity is
+500 MMcf/d with current throughput of ~80 MMcf/d from 15 producer connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>The anchor shipper contract covers 50 MMcf/d at $0.55/Mcf through 2030
+(5 years remaining) with 80% take-or-pay. Remaining ~30 MMcf/d is under
+short-term (1-2 year) gathering agreements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Basin activity is strong with rig counts up 15% YoY. However, producer
+economics are sensitive to WTI and Henry Hub prices. The system has
+expansion capacity without major capex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>The seller (PE fund approaching end of fund life) is asking $85mm with
+bids due by February 10, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>* Volume Trajectory: Producer drilling activity drives throughput</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Take-or-Pay: 80% MVC provides revenue floor on contracted volumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Recontracting Risk: Anchor contract expiry in 2030 is key risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Basin Economics: WTI/HH prices drive producer drilling decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR MIDSTREAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>- Volume-based revenue (not capacity x price)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>- Producer counterparty credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>- Volume decline curves for existing wells</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>- Recontracting risk at contract expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>- Gathering fee is $/Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Y1 Volume: 80 MMcf/d (current throughput)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Gathering Fee: $0.55/Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Growth Rate Y1-5: 3%/year</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Decline Rate Y6-10: 5%/year</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - O&amp;M: $3.5mm/year base</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>2. BUILD VOLUME TRAJECTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Daily Volume Y1 = 80 MMcf/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Daily Volume Yn = Y(n-1) x (1 + Growth/Decline Rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Annual Volume (Bcf) = Daily Volume x 365 / 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="31" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>3. BUILD REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Revenue ($mm) = Annual Volume (Bcf) x Fee ($/Mcf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Why this works:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 1 Bcf = 1,000,000 Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Revenue ($) = Bcf x 1,000,000 x $/Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Revenue ($mm) = Revenue ($) / 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Therefore: Revenue ($mm) = Bcf x $/Mcf (factors cancel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="31" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   NO *1000 multiplier needed!</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="31" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sanity Check: 29 Bcf x $0.55/Mcf = ~$16mm revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   This is reasonable for $85mm EV (5x EV/Revenue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="31" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>4. BUILD CFADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CFADS = Revenue - O&amp;M - Taxes - Growth Capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Growth capex (wellhead connections) is BEFORE CFADS for midstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>5. DEBT STRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   75% cash sweep (volume uncertainty warrants sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Shorter tenor (5 years) due to recontracting risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Same as CCGT - use Scheduled DS for DSRA Target to avoid circularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A. Processing vs Gathering:</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If system includes processing plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Processing revenue is $/MMBtu (different unit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B. Commodity Exposure:</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If fee has commodity-linked component</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Must model WTI/HH price scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C. Acreage Dedication:</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If contract includes acreage dedication</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Provides volume upside if producer drills more</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="29" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1. Revenue formula does NOT have erroneous *1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2. Y1 Revenue / Entry EV = reasonable multiple (4-6x typical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3. Volume trajectory makes sense (growth then decline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4. Take-or-pay floor revenue = MVC x Fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>5. Recontracting scenario modeled for Year 5+</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>6. DSCR &gt;= 1.25x during debt tenor</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="29" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>* Revenue = Bcf x $/Mcf (NO conversion factor - they cancel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="32" t="inlineStr">
+        <is>
+          <t>* Y1 Revenue of ~$16mm on $85mm EV is ~5.3x, reasonable</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="32" t="inlineStr">
+        <is>
+          <t>* Recontracting at Year 5 is THE key risk - show sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="32" t="inlineStr">
+        <is>
+          <t>* Take-or-pay provides 80% floor on contracted volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="29" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Q: Walk me through how you modeled volume decline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Q: What's your recontracting assumption when anchor expires?</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Q: How would a $10/bbl drop in WTI affect volume projections?</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Q: What producer credit diligence would you conduct?</t>
         </is>
       </c>
     </row>
@@ -1079,38 +1666,60 @@
           <t>Midstream Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -2157,7 +2766,6 @@
         <v/>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +100,12 @@
       <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -151,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -210,6 +216,14 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1239,7 +1253,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -1261,7 +1274,6 @@
         </is>
       </c>
     </row>
-    <row r="82"/>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
@@ -1283,7 +1295,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -1319,7 +1330,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -1882,7 +1892,6 @@
           <t>4:00</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="36" t="inlineStr">
@@ -3507,216 +3516,196 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="46" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="47" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-      <c r="D15" s="7">
-        <f>AVERAGE(E68:I68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>IF(COUNTIF(E79:I79,"&gt;0")&gt;0,MINIFS(E79:I79,E79:I79,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D17" s="23">
-        <f>D113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Total In / Total Out</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>D114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D19" s="23">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -3729,9 +3718,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -3771,8 +3760,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3873,7 +3860,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -3954,7 +3940,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -4015,7 +4000,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -4096,7 +4080,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -4237,7 +4220,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -4318,7 +4300,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
@@ -4402,7 +4383,6 @@
         <v/>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -4594,7 +4574,6 @@
         <v/>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
@@ -4709,7 +4688,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -4767,7 +4745,6 @@
         <v/>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -5016,7 +4993,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -5603,7 +5579,6 @@
         <v/>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -6051,7 +6026,6 @@
         <v/>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
@@ -6149,7 +6123,6 @@
         <v/>
       </c>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="A109" s="21" t="inlineStr">
         <is>
@@ -6227,7 +6200,6 @@
         <v/>
       </c>
     </row>
-    <row r="114"/>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
@@ -6332,7 +6304,6 @@
         <v/>
       </c>
     </row>
-    <row r="120"/>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
@@ -6452,7 +6423,6 @@
         <v/>
       </c>
     </row>
-    <row r="125"/>
     <row r="126">
       <c r="A126" s="21" t="inlineStr">
         <is>
@@ -6709,216 +6679,196 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="46" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="47" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-      <c r="D15" s="7">
-        <f>AVERAGE(E68:I68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>IF(COUNTIF(E79:I79,"&gt;0")&gt;0,MINIFS(E79:I79,E79:I79,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D17" s="23">
-        <f>D113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Total In / Total Out</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>D114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D19" s="23">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -6931,9 +6881,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -6973,8 +6923,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -7075,7 +7023,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -7156,7 +7103,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -7217,7 +7163,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -7298,7 +7243,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -7439,7 +7383,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -7520,7 +7463,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
@@ -7604,7 +7546,6 @@
         <v/>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -7796,7 +7737,6 @@
         <v/>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
@@ -7911,7 +7851,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -7969,7 +7908,6 @@
         <v/>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -8218,7 +8156,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -8805,7 +8742,6 @@
         <v/>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -9253,7 +9189,6 @@
         <v/>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
@@ -9351,7 +9286,6 @@
         <v/>
       </c>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="A109" s="21" t="inlineStr">
         <is>
@@ -9429,7 +9363,6 @@
         <v/>
       </c>
     </row>
-    <row r="114"/>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
@@ -9590,7 +9523,6 @@
         </is>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
@@ -9710,7 +9642,6 @@
         <v/>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" s="21" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +106,14 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -157,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,6 +232,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3491,6 +3501,11 @@
         <f>$D$17</f>
         <v/>
       </c>
+      <c r="M3" s="50" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3511,6 +3526,11 @@
       <c r="D4" s="7">
         <f>E62</f>
         <v/>
+      </c>
+      <c r="M4" s="51" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3522,6 +3542,11 @@
       <c r="B5" s="44" t="n"/>
       <c r="C5" s="44" t="n"/>
       <c r="D5" s="44" t="n"/>
+      <c r="M5" s="51" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="44" t="n"/>
@@ -3760,6 +3785,8 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3860,6 +3887,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -3940,6 +3968,7 @@
         <v>0.05</v>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -4000,6 +4029,7 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -4080,6 +4110,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -4220,6 +4251,7 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -4300,6 +4332,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
@@ -4383,6 +4416,7 @@
         <v/>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -4574,6 +4608,7 @@
         <v/>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
@@ -4688,6 +4723,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -4745,6 +4781,7 @@
         <v/>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -4993,6 +5030,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -5579,6 +5617,7 @@
         <v/>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -6026,6 +6065,7 @@
         <v/>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
@@ -6123,6 +6163,7 @@
         <v/>
       </c>
     </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" s="21" t="inlineStr">
         <is>
@@ -6200,6 +6241,7 @@
         <v/>
       </c>
     </row>
+    <row r="114"/>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
@@ -6304,6 +6346,7 @@
         <v/>
       </c>
     </row>
+    <row r="120"/>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
@@ -6423,6 +6466,7 @@
         <v/>
       </c>
     </row>
+    <row r="125"/>
     <row r="126">
       <c r="A126" s="21" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,6 +234,7 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3380,7 +3381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3498,7 +3499,7 @@
         </is>
       </c>
       <c r="D3" s="7">
-        <f>$D$17</f>
+        <f>$D$27</f>
         <v/>
       </c>
       <c r="M3" s="50" t="inlineStr">
@@ -3524,7 +3525,7 @@
         </is>
       </c>
       <c r="D4" s="7">
-        <f>E62</f>
+        <f>E72</f>
         <v/>
       </c>
       <c r="M4" s="51" t="inlineStr">
@@ -3785,8 +3786,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3887,7 +3886,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -3968,7 +3966,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -4029,7 +4026,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -4110,7 +4106,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -4251,7 +4246,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -4332,7 +4326,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
@@ -4370,7 +4363,7 @@
         </is>
       </c>
       <c r="D60" s="16">
-        <f>$D$17*$D$37</f>
+        <f>$D$27*$D$47</f>
         <v/>
       </c>
     </row>
@@ -4391,7 +4384,7 @@
         </is>
       </c>
       <c r="D61" s="16">
-        <f>$D$17*$D$46/$D$47</f>
+        <f>$D$27*$D$56/$D$57</f>
         <v/>
       </c>
     </row>
@@ -4412,11 +4405,10 @@
         </is>
       </c>
       <c r="D62" s="16">
-        <f>$D$50/$D$39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63"/>
+        <f>$D$60/$D$49</f>
+        <v/>
+      </c>
+    </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -4454,43 +4446,43 @@
         </is>
       </c>
       <c r="E65" s="17">
-        <f>$D$23*(1+$D$24)^(1-1)</f>
+        <f>$D$33*(1+$D$34)^(1-1)</f>
         <v/>
       </c>
       <c r="F65" s="17">
-        <f>$D$23*(1+$D$24)^(2-1)</f>
+        <f>$D$33*(1+$D$34)^(2-1)</f>
         <v/>
       </c>
       <c r="G65" s="17">
-        <f>$D$23*(1+$D$24)^(3-1)</f>
+        <f>$D$33*(1+$D$34)^(3-1)</f>
         <v/>
       </c>
       <c r="H65" s="17">
-        <f>$D$23*(1+$D$24)^(4-1)</f>
+        <f>$D$33*(1+$D$34)^(4-1)</f>
         <v/>
       </c>
       <c r="I65" s="17">
-        <f>$D$23*(1+$D$24)^(5-1)</f>
+        <f>$D$33*(1+$D$34)^(5-1)</f>
         <v/>
       </c>
       <c r="J65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(6-5)</f>
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(6-5)</f>
         <v/>
       </c>
       <c r="K65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(7-5)</f>
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(7-5)</f>
         <v/>
       </c>
       <c r="L65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(8-5)</f>
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(8-5)</f>
         <v/>
       </c>
       <c r="M65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(9-5)</f>
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(9-5)</f>
         <v/>
       </c>
       <c r="N65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(10-5)</f>
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(10-5)</f>
         <v/>
       </c>
     </row>
@@ -4511,43 +4503,43 @@
         </is>
       </c>
       <c r="E66" s="17">
-        <f>E55*365/1000</f>
+        <f>E65*365</f>
         <v/>
       </c>
       <c r="F66" s="17">
-        <f>F55*365/1000</f>
+        <f>F65*365</f>
         <v/>
       </c>
       <c r="G66" s="17">
-        <f>G55*365/1000</f>
+        <f>G65*365</f>
         <v/>
       </c>
       <c r="H66" s="17">
-        <f>H55*365/1000</f>
+        <f>H65*365</f>
         <v/>
       </c>
       <c r="I66" s="17">
-        <f>I55*365/1000</f>
+        <f>I65*365</f>
         <v/>
       </c>
       <c r="J66" s="17">
-        <f>J55*365/1000</f>
+        <f>J65*365</f>
         <v/>
       </c>
       <c r="K66" s="17">
-        <f>K55*365/1000</f>
+        <f>K65*365</f>
         <v/>
       </c>
       <c r="L66" s="17">
-        <f>L55*365/1000</f>
+        <f>L65*365</f>
         <v/>
       </c>
       <c r="M66" s="17">
-        <f>M55*365/1000</f>
+        <f>M65*365</f>
         <v/>
       </c>
       <c r="N66" s="17">
-        <f>N55*365/1000</f>
+        <f>N65*365</f>
         <v/>
       </c>
     </row>
@@ -4568,47 +4560,46 @@
         </is>
       </c>
       <c r="E67" s="18">
-        <f>$D$28*(1+$D$29)^(1-1)</f>
+        <f>$D$38*(1+$D$39)^(1-1)</f>
         <v/>
       </c>
       <c r="F67" s="18">
-        <f>$D$28*(1+$D$29)^(2-1)</f>
+        <f>$D$38*(1+$D$39)^(2-1)</f>
         <v/>
       </c>
       <c r="G67" s="18">
-        <f>$D$28*(1+$D$29)^(3-1)</f>
+        <f>$D$38*(1+$D$39)^(3-1)</f>
         <v/>
       </c>
       <c r="H67" s="18">
-        <f>$D$28*(1+$D$29)^(4-1)</f>
+        <f>$D$38*(1+$D$39)^(4-1)</f>
         <v/>
       </c>
       <c r="I67" s="18">
-        <f>$D$28*(1+$D$29)^(5-1)</f>
+        <f>$D$38*(1+$D$39)^(5-1)</f>
         <v/>
       </c>
       <c r="J67" s="18">
-        <f>$D$28*(1+$D$29)^(6-1)</f>
+        <f>$D$38*(1+$D$39)^(6-1)</f>
         <v/>
       </c>
       <c r="K67" s="18">
-        <f>$D$28*(1+$D$29)^(7-1)</f>
+        <f>$D$38*(1+$D$39)^(7-1)</f>
         <v/>
       </c>
       <c r="L67" s="18">
-        <f>$D$28*(1+$D$29)^(8-1)</f>
+        <f>$D$38*(1+$D$39)^(8-1)</f>
         <v/>
       </c>
       <c r="M67" s="18">
-        <f>$D$28*(1+$D$29)^(9-1)</f>
+        <f>$D$38*(1+$D$39)^(9-1)</f>
         <v/>
       </c>
       <c r="N67" s="18">
-        <f>$D$28*(1+$D$29)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68"/>
+        <f>$D$38*(1+$D$39)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
@@ -4626,43 +4617,43 @@
         </is>
       </c>
       <c r="E69" s="16">
-        <f>E56*E57</f>
+        <f>E66*E67</f>
         <v/>
       </c>
       <c r="F69" s="16">
-        <f>F56*F57</f>
+        <f>F66*F67</f>
         <v/>
       </c>
       <c r="G69" s="16">
-        <f>G56*G57</f>
+        <f>G66*G67</f>
         <v/>
       </c>
       <c r="H69" s="16">
-        <f>H56*H57</f>
+        <f>H66*H67</f>
         <v/>
       </c>
       <c r="I69" s="16">
-        <f>I56*I57</f>
+        <f>I66*I67</f>
         <v/>
       </c>
       <c r="J69" s="16">
-        <f>J56*J57</f>
+        <f>J66*J67</f>
         <v/>
       </c>
       <c r="K69" s="16">
-        <f>K56*K57</f>
+        <f>K66*K67</f>
         <v/>
       </c>
       <c r="L69" s="16">
-        <f>L56*L57</f>
+        <f>L66*L67</f>
         <v/>
       </c>
       <c r="M69" s="16">
-        <f>M56*M57</f>
+        <f>M66*M67</f>
         <v/>
       </c>
       <c r="N69" s="16">
-        <f>N56*N57</f>
+        <f>N66*N67</f>
         <v/>
       </c>
     </row>
@@ -4683,47 +4674,46 @@
         </is>
       </c>
       <c r="E70" s="16">
-        <f>$D$32*(1+$D$33)^(1-1)</f>
+        <f>$D$42*(1+$D$43)^(1-1)</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>$D$32*(1+$D$33)^(2-1)</f>
+        <f>$D$42*(1+$D$43)^(2-1)</f>
         <v/>
       </c>
       <c r="G70" s="16">
-        <f>$D$32*(1+$D$33)^(3-1)</f>
+        <f>$D$42*(1+$D$43)^(3-1)</f>
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>$D$32*(1+$D$33)^(4-1)</f>
+        <f>$D$42*(1+$D$43)^(4-1)</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>$D$32*(1+$D$33)^(5-1)</f>
+        <f>$D$42*(1+$D$43)^(5-1)</f>
         <v/>
       </c>
       <c r="J70" s="16">
-        <f>$D$32*(1+$D$33)^(6-1)</f>
+        <f>$D$42*(1+$D$43)^(6-1)</f>
         <v/>
       </c>
       <c r="K70" s="16">
-        <f>$D$32*(1+$D$33)^(7-1)</f>
+        <f>$D$42*(1+$D$43)^(7-1)</f>
         <v/>
       </c>
       <c r="L70" s="16">
-        <f>$D$32*(1+$D$33)^(8-1)</f>
+        <f>$D$42*(1+$D$43)^(8-1)</f>
         <v/>
       </c>
       <c r="M70" s="16">
-        <f>$D$32*(1+$D$33)^(9-1)</f>
+        <f>$D$42*(1+$D$43)^(9-1)</f>
         <v/>
       </c>
       <c r="N70" s="16">
-        <f>$D$32*(1+$D$33)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71"/>
+        <f>$D$42*(1+$D$43)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -4741,47 +4731,46 @@
         </is>
       </c>
       <c r="E72" s="7">
-        <f>E59-E60</f>
+        <f>E69-E70</f>
         <v/>
       </c>
       <c r="F72" s="7">
-        <f>F59-F60</f>
+        <f>F69-F70</f>
         <v/>
       </c>
       <c r="G72" s="7">
-        <f>G59-G60</f>
+        <f>G69-G70</f>
         <v/>
       </c>
       <c r="H72" s="7">
-        <f>H59-H60</f>
+        <f>H69-H70</f>
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>I59-I60</f>
+        <f>I69-I70</f>
         <v/>
       </c>
       <c r="J72" s="7">
-        <f>J59-J60</f>
+        <f>J69-J70</f>
         <v/>
       </c>
       <c r="K72" s="7">
-        <f>K59-K60</f>
+        <f>K69-K70</f>
         <v/>
       </c>
       <c r="L72" s="7">
-        <f>L59-L60</f>
+        <f>L69-L70</f>
         <v/>
       </c>
       <c r="M72" s="7">
-        <f>M59-M60</f>
+        <f>M69-M70</f>
         <v/>
       </c>
       <c r="N72" s="7">
-        <f>N59-N60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73"/>
+        <f>N69-N70</f>
+        <v/>
+      </c>
+    </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -4819,43 +4808,43 @@
         </is>
       </c>
       <c r="E75" s="16">
-        <f>E62-$D$51</f>
+        <f>MAX(0,E72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>F62-$D$51</f>
+        <f>MAX(0,F72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="G75" s="16">
-        <f>G62-$D$51</f>
+        <f>MAX(0,G72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>H62-$D$51</f>
+        <f>MAX(0,H72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>I62-$D$51</f>
+        <f>MAX(0,I72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="J75" s="16">
-        <f>J62-$D$51</f>
+        <f>MAX(0,J72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="K75" s="16">
-        <f>K62-$D$51</f>
+        <f>MAX(0,K72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="L75" s="16">
-        <f>L62-$D$51</f>
+        <f>MAX(0,L72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="M75" s="16">
-        <f>M62-$D$51</f>
+        <f>MAX(0,M72-$D$61)*$D$55</f>
         <v/>
       </c>
       <c r="N75" s="16">
-        <f>N62-$D$51</f>
+        <f>MAX(0,N72-$D$61)*$D$55</f>
         <v/>
       </c>
     </row>
@@ -4876,43 +4865,43 @@
         </is>
       </c>
       <c r="E76" s="16">
-        <f>MAX(0,E65)*$D$45</f>
+        <f>IF(1&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>MAX(0,F65)*$D$45</f>
+        <f>IF(2&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="G76" s="16">
-        <f>MAX(0,G65)*$D$45</f>
+        <f>IF(3&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>MAX(0,H65)*$D$45</f>
+        <f>IF(4&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>MAX(0,I65)*$D$45</f>
+        <f>IF(5&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="J76" s="16">
-        <f>MAX(0,J65)*$D$45</f>
+        <f>IF(6&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="K76" s="16">
-        <f>MAX(0,K65)*$D$45</f>
+        <f>IF(7&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="L76" s="16">
-        <f>MAX(0,L65)*$D$45</f>
+        <f>IF(8&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="M76" s="16">
-        <f>MAX(0,M65)*$D$45</f>
+        <f>IF(9&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="N76" s="16">
-        <f>MAX(0,N65)*$D$45</f>
+        <f>IF(10&lt;=5,$D$44,0)</f>
         <v/>
       </c>
     </row>
@@ -4932,44 +4921,44 @@
           <t>Y1-Y5 only</t>
         </is>
       </c>
-      <c r="E77" s="19">
-        <f>IF(1&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="F77" s="19">
-        <f>IF(2&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="G77" s="19">
-        <f>IF(3&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="H77" s="19">
-        <f>IF(4&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="I77" s="19">
-        <f>IF(5&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="J77" s="19">
-        <f>IF(6&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="K77" s="19">
-        <f>IF(7&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="L77" s="19">
-        <f>IF(8&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="M77" s="19">
-        <f>IF(9&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="N77" s="19">
-        <f>IF(10&lt;=5,$D$34,0)</f>
+      <c r="E77" s="7">
+        <f>E72-E75-E76</f>
+        <v/>
+      </c>
+      <c r="F77" s="7">
+        <f>F72-F75-F76</f>
+        <v/>
+      </c>
+      <c r="G77" s="7">
+        <f>G72-G75-G76</f>
+        <v/>
+      </c>
+      <c r="H77" s="7">
+        <f>H72-H75-H76</f>
+        <v/>
+      </c>
+      <c r="I77" s="7">
+        <f>I72-I75-I76</f>
+        <v/>
+      </c>
+      <c r="J77" s="7">
+        <f>J72-J75-J76</f>
+        <v/>
+      </c>
+      <c r="K77" s="7">
+        <f>K72-K75-K76</f>
+        <v/>
+      </c>
+      <c r="L77" s="7">
+        <f>L72-L75-L76</f>
+        <v/>
+      </c>
+      <c r="M77" s="7">
+        <f>M72-M75-M76</f>
+        <v/>
+      </c>
+      <c r="N77" s="7">
+        <f>N72-N75-N76</f>
         <v/>
       </c>
     </row>
@@ -5030,7 +5019,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -5063,44 +5051,47 @@
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr"/>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
       <c r="E81" s="16">
-        <f>$D$50</f>
+        <f>$D$60</f>
         <v/>
       </c>
       <c r="F81" s="16">
-        <f>E78</f>
+        <f>E88</f>
         <v/>
       </c>
       <c r="G81" s="16">
-        <f>F78</f>
+        <f>F88</f>
         <v/>
       </c>
       <c r="H81" s="16">
-        <f>G78</f>
+        <f>G88</f>
         <v/>
       </c>
       <c r="I81" s="16">
-        <f>H78</f>
+        <f>H88</f>
         <v/>
       </c>
       <c r="J81" s="16">
-        <f>I78</f>
+        <f>I88</f>
         <v/>
       </c>
       <c r="K81" s="16">
-        <f>J78</f>
+        <f>J88</f>
         <v/>
       </c>
       <c r="L81" s="16">
-        <f>K78</f>
+        <f>K88</f>
         <v/>
       </c>
       <c r="M81" s="16">
-        <f>L78</f>
+        <f>L88</f>
         <v/>
       </c>
       <c r="N81" s="16">
-        <f>M78</f>
+        <f>M88</f>
         <v/>
       </c>
     </row>
@@ -5121,43 +5112,43 @@
         </is>
       </c>
       <c r="E82" s="16">
-        <f>E71*$D$38</f>
+        <f>E81*$D$48</f>
         <v/>
       </c>
       <c r="F82" s="16">
-        <f>F71*$D$38</f>
+        <f>F81*$D$48</f>
         <v/>
       </c>
       <c r="G82" s="16">
-        <f>G71*$D$38</f>
+        <f>G81*$D$48</f>
         <v/>
       </c>
       <c r="H82" s="16">
-        <f>H71*$D$38</f>
+        <f>H81*$D$48</f>
         <v/>
       </c>
       <c r="I82" s="16">
-        <f>I71*$D$38</f>
+        <f>I81*$D$48</f>
         <v/>
       </c>
       <c r="J82" s="16">
-        <f>J71*$D$38</f>
+        <f>J81*$D$48</f>
         <v/>
       </c>
       <c r="K82" s="16">
-        <f>K71*$D$38</f>
+        <f>K81*$D$48</f>
         <v/>
       </c>
       <c r="L82" s="16">
-        <f>L71*$D$38</f>
+        <f>L81*$D$48</f>
         <v/>
       </c>
       <c r="M82" s="16">
-        <f>M71*$D$38</f>
+        <f>M81*$D$48</f>
         <v/>
       </c>
       <c r="N82" s="16">
-        <f>N71*$D$38</f>
+        <f>N81*$D$48</f>
         <v/>
       </c>
     </row>
@@ -5178,43 +5169,43 @@
         </is>
       </c>
       <c r="E83" s="16">
-        <f>MIN($D$52,E71)</f>
+        <f>MIN($D$62,E81)</f>
         <v/>
       </c>
       <c r="F83" s="16">
-        <f>MIN($D$52,F71)</f>
+        <f>MIN($D$62,F81)</f>
         <v/>
       </c>
       <c r="G83" s="16">
-        <f>MIN($D$52,G71)</f>
+        <f>MIN($D$62,G81)</f>
         <v/>
       </c>
       <c r="H83" s="16">
-        <f>MIN($D$52,H71)</f>
+        <f>MIN($D$62,H81)</f>
         <v/>
       </c>
       <c r="I83" s="16">
-        <f>MIN($D$52,I71)</f>
+        <f>MIN($D$62,I81)</f>
         <v/>
       </c>
       <c r="J83" s="16">
-        <f>MIN($D$52,J71)</f>
+        <f>MIN($D$62,J81)</f>
         <v/>
       </c>
       <c r="K83" s="16">
-        <f>MIN($D$52,K71)</f>
+        <f>MIN($D$62,K81)</f>
         <v/>
       </c>
       <c r="L83" s="16">
-        <f>MIN($D$52,L71)</f>
+        <f>MIN($D$62,L81)</f>
         <v/>
       </c>
       <c r="M83" s="16">
-        <f>MIN($D$52,M71)</f>
+        <f>MIN($D$62,M81)</f>
         <v/>
       </c>
       <c r="N83" s="16">
-        <f>MIN($D$52,N71)</f>
+        <f>MIN($D$62,N81)</f>
         <v/>
       </c>
     </row>
@@ -5235,43 +5226,43 @@
         </is>
       </c>
       <c r="E84" s="16">
-        <f>E72+E73</f>
+        <f>E82+E83</f>
         <v/>
       </c>
       <c r="F84" s="16">
-        <f>F72+F73</f>
+        <f>F82+F83</f>
         <v/>
       </c>
       <c r="G84" s="16">
-        <f>G72+G73</f>
+        <f>G82+G83</f>
         <v/>
       </c>
       <c r="H84" s="16">
-        <f>H72+H73</f>
+        <f>H82+H83</f>
         <v/>
       </c>
       <c r="I84" s="16">
-        <f>I72+I73</f>
+        <f>I82+I83</f>
         <v/>
       </c>
       <c r="J84" s="16">
-        <f>J72+J73</f>
+        <f>J82+J83</f>
         <v/>
       </c>
       <c r="K84" s="16">
-        <f>K72+K73</f>
+        <f>K82+K83</f>
         <v/>
       </c>
       <c r="L84" s="16">
-        <f>L72+L73</f>
+        <f>L82+L83</f>
         <v/>
       </c>
       <c r="M84" s="16">
-        <f>M72+M73</f>
+        <f>M82+M83</f>
         <v/>
       </c>
       <c r="N84" s="16">
-        <f>N72+N73</f>
+        <f>N82+N83</f>
         <v/>
       </c>
     </row>
@@ -5292,43 +5283,43 @@
         </is>
       </c>
       <c r="E85" s="16">
-        <f>MAX(0,E68-E74-E85)</f>
+        <f>MAX(0,E77-E84-E96)</f>
         <v/>
       </c>
       <c r="F85" s="16">
-        <f>MAX(0,F68-F74-F85)</f>
+        <f>MAX(0,F77-F84-F96)</f>
         <v/>
       </c>
       <c r="G85" s="16">
-        <f>MAX(0,G68-G74-G85)</f>
+        <f>MAX(0,G77-G84-G96)</f>
         <v/>
       </c>
       <c r="H85" s="16">
-        <f>MAX(0,H68-H74-H85)</f>
+        <f>MAX(0,H77-H84-H96)</f>
         <v/>
       </c>
       <c r="I85" s="16">
-        <f>MAX(0,I68-I74-I85)</f>
+        <f>MAX(0,I77-I84-I96)</f>
         <v/>
       </c>
       <c r="J85" s="16">
-        <f>MAX(0,J68-J74-J85)</f>
+        <f>MAX(0,J77-J84-J96)</f>
         <v/>
       </c>
       <c r="K85" s="16">
-        <f>MAX(0,K68-K74-K85)</f>
+        <f>MAX(0,K77-K84-K96)</f>
         <v/>
       </c>
       <c r="L85" s="16">
-        <f>MAX(0,L68-L74-L85)</f>
+        <f>MAX(0,L77-L84-L96)</f>
         <v/>
       </c>
       <c r="M85" s="16">
-        <f>MAX(0,M68-M74-M85)</f>
+        <f>MAX(0,M77-M84-M96)</f>
         <v/>
       </c>
       <c r="N85" s="16">
-        <f>MAX(0,N68-N74-N85)</f>
+        <f>MAX(0,N77-N84-N96)</f>
         <v/>
       </c>
     </row>
@@ -5349,43 +5340,43 @@
         </is>
       </c>
       <c r="E86" s="19">
-        <f>MIN(MAX(0,E75)*$D$41,MAX(0,E71-E73))</f>
+        <f>MIN(E85*$D$51,MAX(0,E81-E83))</f>
         <v/>
       </c>
       <c r="F86" s="19">
-        <f>MIN(MAX(0,F75)*$D$41,MAX(0,F71-F73))</f>
+        <f>MIN(F85*$D$51,MAX(0,F81-F83))</f>
         <v/>
       </c>
       <c r="G86" s="19">
-        <f>MIN(MAX(0,G75)*$D$41,MAX(0,G71-G73))</f>
+        <f>MIN(G85*$D$51,MAX(0,G81-G83))</f>
         <v/>
       </c>
       <c r="H86" s="19">
-        <f>MIN(MAX(0,H75)*$D$41,MAX(0,H71-H73))</f>
+        <f>MIN(H85*$D$51,MAX(0,H81-H83))</f>
         <v/>
       </c>
       <c r="I86" s="19">
-        <f>MIN(MAX(0,I75)*$D$41,MAX(0,I71-I73))</f>
+        <f>MIN(I85*$D$51,MAX(0,I81-I83))</f>
         <v/>
       </c>
       <c r="J86" s="19">
-        <f>MIN(MAX(0,J75)*$D$41,MAX(0,J71-J73))</f>
+        <f>MIN(J85*$D$51,MAX(0,J81-J83))</f>
         <v/>
       </c>
       <c r="K86" s="19">
-        <f>MIN(MAX(0,K75)*$D$41,MAX(0,K71-K73))</f>
+        <f>MIN(K85*$D$51,MAX(0,K81-K83))</f>
         <v/>
       </c>
       <c r="L86" s="19">
-        <f>MIN(MAX(0,L75)*$D$41,MAX(0,L71-L73))</f>
+        <f>MIN(L85*$D$51,MAX(0,L81-L83))</f>
         <v/>
       </c>
       <c r="M86" s="19">
-        <f>MIN(MAX(0,M75)*$D$41,MAX(0,M71-M73))</f>
+        <f>MIN(M85*$D$51,MAX(0,M81-M83))</f>
         <v/>
       </c>
       <c r="N86" s="19">
-        <f>MIN(MAX(0,N75)*$D$41,MAX(0,N71-N73))</f>
+        <f>MIN(N85*$D$51,MAX(0,N81-N83))</f>
         <v/>
       </c>
     </row>
@@ -5406,43 +5397,43 @@
         </is>
       </c>
       <c r="E87" s="16">
-        <f>E73+E76</f>
+        <f>E83+E86</f>
         <v/>
       </c>
       <c r="F87" s="16">
-        <f>F73+F76</f>
+        <f>F83+F86</f>
         <v/>
       </c>
       <c r="G87" s="16">
-        <f>G73+G76</f>
+        <f>G83+G86</f>
         <v/>
       </c>
       <c r="H87" s="16">
-        <f>H73+H76</f>
+        <f>H83+H86</f>
         <v/>
       </c>
       <c r="I87" s="16">
-        <f>I73+I76</f>
+        <f>I83+I86</f>
         <v/>
       </c>
       <c r="J87" s="16">
-        <f>J73+J76</f>
+        <f>J83+J86</f>
         <v/>
       </c>
       <c r="K87" s="16">
-        <f>K73+K76</f>
+        <f>K83+K86</f>
         <v/>
       </c>
       <c r="L87" s="16">
-        <f>L73+L76</f>
+        <f>L83+L86</f>
         <v/>
       </c>
       <c r="M87" s="16">
-        <f>M73+M76</f>
+        <f>M83+M86</f>
         <v/>
       </c>
       <c r="N87" s="16">
-        <f>N73+N76</f>
+        <f>N83+N86</f>
         <v/>
       </c>
     </row>
@@ -5462,44 +5453,48 @@
           <t>MAX(0, Beg - Total Prin)</t>
         </is>
       </c>
+      <c r="D88">
+        <f>$D$60</f>
+        <v/>
+      </c>
       <c r="E88" s="16">
-        <f>MAX(0,E71-E77)</f>
+        <f>MAX(0,E81-E87)</f>
         <v/>
       </c>
       <c r="F88" s="16">
-        <f>MAX(0,F71-F77)</f>
+        <f>MAX(0,F81-F87)</f>
         <v/>
       </c>
       <c r="G88" s="16">
-        <f>MAX(0,G71-G77)</f>
+        <f>MAX(0,G81-G87)</f>
         <v/>
       </c>
       <c r="H88" s="16">
-        <f>MAX(0,H71-H77)</f>
+        <f>MAX(0,H81-H87)</f>
         <v/>
       </c>
       <c r="I88" s="16">
-        <f>MAX(0,I71-I77)</f>
+        <f>MAX(0,I81-I87)</f>
         <v/>
       </c>
       <c r="J88" s="16">
-        <f>MAX(0,J71-J77)</f>
+        <f>MAX(0,J81-J87)</f>
         <v/>
       </c>
       <c r="K88" s="16">
-        <f>MAX(0,K71-K77)</f>
+        <f>MAX(0,K81-K87)</f>
         <v/>
       </c>
       <c r="L88" s="16">
-        <f>MAX(0,L71-L77)</f>
+        <f>MAX(0,L81-L87)</f>
         <v/>
       </c>
       <c r="M88" s="16">
-        <f>MAX(0,M71-M77)</f>
+        <f>MAX(0,M81-M87)</f>
         <v/>
       </c>
       <c r="N88" s="16">
-        <f>MAX(0,N71-N77)</f>
+        <f>MAX(0,N81-N87)</f>
         <v/>
       </c>
     </row>
@@ -5520,43 +5515,43 @@
         </is>
       </c>
       <c r="E89" s="22">
-        <f>IF(E74&gt;0,E68/E74,0)</f>
+        <f>IF(E84&gt;0,E77/E84,0)</f>
         <v/>
       </c>
       <c r="F89" s="22">
-        <f>IF(F74&gt;0,F68/F74,0)</f>
+        <f>IF(F84&gt;0,F77/F84,0)</f>
         <v/>
       </c>
       <c r="G89" s="22">
-        <f>IF(G74&gt;0,G68/G74,0)</f>
+        <f>IF(G84&gt;0,G77/G84,0)</f>
         <v/>
       </c>
       <c r="H89" s="22">
-        <f>IF(H74&gt;0,H68/H74,0)</f>
+        <f>IF(H84&gt;0,H77/H84,0)</f>
         <v/>
       </c>
       <c r="I89" s="22">
-        <f>IF(I74&gt;0,I68/I74,0)</f>
+        <f>IF(I84&gt;0,I77/I84,0)</f>
         <v/>
       </c>
       <c r="J89" s="22">
-        <f>IF(J74&gt;0,J68/J74,0)</f>
+        <f>IF(J84&gt;0,J77/J84,0)</f>
         <v/>
       </c>
       <c r="K89" s="22">
-        <f>IF(K74&gt;0,K68/K74,0)</f>
+        <f>IF(K84&gt;0,K77/K84,0)</f>
         <v/>
       </c>
       <c r="L89" s="22">
-        <f>IF(L74&gt;0,L68/L74,0)</f>
+        <f>IF(L84&gt;0,L77/L84,0)</f>
         <v/>
       </c>
       <c r="M89" s="22">
-        <f>IF(M74&gt;0,M68/M74,0)</f>
+        <f>IF(M84&gt;0,M77/M84,0)</f>
         <v/>
       </c>
       <c r="N89" s="22">
-        <f>IF(N74&gt;0,N68/N74,0)</f>
+        <f>IF(N84&gt;0,N77/N84,0)</f>
         <v/>
       </c>
     </row>
@@ -5577,47 +5572,46 @@
         </is>
       </c>
       <c r="E90" s="16">
-        <f>MAX(0,$D$50-(1-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(1-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="F90" s="16">
-        <f>MAX(0,$D$50-(2-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(2-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="G90" s="16">
-        <f>MAX(0,$D$50-(3-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(3-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="H90" s="16">
-        <f>MAX(0,$D$50-(4-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(4-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="I90" s="16">
-        <f>MAX(0,$D$50-(5-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(5-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="J90" s="16">
-        <f>MAX(0,$D$50-(6-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(6-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="K90" s="16">
-        <f>MAX(0,$D$50-(7-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(7-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="L90" s="16">
-        <f>MAX(0,$D$50-(8-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(8-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="M90" s="16">
-        <f>MAX(0,$D$50-(9-1)*$D$52)*$D$38+$D$52</f>
+        <f>MAX(0,$D$60-(9-1)*$D$62)*$D$48+$D$62</f>
         <v/>
       </c>
       <c r="N90" s="16">
-        <f>MAX(0,$D$50-(10-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91"/>
+        <f>MAX(0,$D$60-(10-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+    </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -5716,44 +5710,43 @@
         <v/>
       </c>
       <c r="E94" s="16">
-        <f>D86</f>
+        <f>F90*$D$50/12</f>
         <v/>
       </c>
       <c r="F94" s="16">
-        <f>E86</f>
+        <f>G90*$D$50/12</f>
         <v/>
       </c>
       <c r="G94" s="16">
-        <f>F86</f>
+        <f>H90*$D$50/12</f>
         <v/>
       </c>
       <c r="H94" s="16">
-        <f>G86</f>
+        <f>I90*$D$50/12</f>
         <v/>
       </c>
       <c r="I94" s="16">
-        <f>H86</f>
+        <f>J90*$D$50/12</f>
         <v/>
       </c>
       <c r="J94" s="16">
-        <f>I86</f>
+        <f>K90*$D$50/12</f>
         <v/>
       </c>
       <c r="K94" s="16">
-        <f>J86</f>
+        <f>L90*$D$50/12</f>
         <v/>
       </c>
       <c r="L94" s="16">
-        <f>K86</f>
+        <f>M90*$D$50/12</f>
         <v/>
       </c>
       <c r="M94" s="16">
-        <f>L86</f>
-        <v/>
-      </c>
-      <c r="N94" s="16">
-        <f>M86</f>
-        <v/>
+        <f>N90*$D$50/12</f>
+        <v/>
+      </c>
+      <c r="N94" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5772,48 +5765,47 @@
           <t>Target - Beginning</t>
         </is>
       </c>
-      <c r="D95" s="16">
-        <f>D83-D84</f>
-        <v/>
+      <c r="D95" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E95" s="16">
-        <f>E83-E84</f>
+        <f>D108</f>
         <v/>
       </c>
       <c r="F95" s="16">
-        <f>F83-F84</f>
+        <f>E97</f>
         <v/>
       </c>
       <c r="G95" s="16">
-        <f>G83-G84</f>
+        <f>F97</f>
         <v/>
       </c>
       <c r="H95" s="16">
-        <f>H83-H84</f>
+        <f>G97</f>
         <v/>
       </c>
       <c r="I95" s="16">
-        <f>I83-I84</f>
+        <f>H97</f>
         <v/>
       </c>
       <c r="J95" s="16">
-        <f>J83-J84</f>
+        <f>I97</f>
         <v/>
       </c>
       <c r="K95" s="16">
-        <f>K83-K84</f>
+        <f>J97</f>
         <v/>
       </c>
       <c r="L95" s="16">
-        <f>L83-L84</f>
+        <f>K97</f>
         <v/>
       </c>
       <c r="M95" s="16">
-        <f>M83-M84</f>
+        <f>L97</f>
         <v/>
       </c>
       <c r="N95" s="16">
-        <f>N83-N84</f>
+        <f>M97</f>
         <v/>
       </c>
     </row>
@@ -5838,43 +5830,43 @@
         <v/>
       </c>
       <c r="E96" s="16">
-        <f>E84+E85</f>
+        <f>E94-E95</f>
         <v/>
       </c>
       <c r="F96" s="16">
-        <f>F84+F85</f>
+        <f>F94-F95</f>
         <v/>
       </c>
       <c r="G96" s="16">
-        <f>G84+G85</f>
+        <f>G94-G95</f>
         <v/>
       </c>
       <c r="H96" s="16">
-        <f>H84+H85</f>
+        <f>H94-H95</f>
         <v/>
       </c>
       <c r="I96" s="16">
-        <f>I84+I85</f>
+        <f>I94-I95</f>
         <v/>
       </c>
       <c r="J96" s="16">
-        <f>J84+J85</f>
+        <f>J94-J95</f>
         <v/>
       </c>
       <c r="K96" s="16">
-        <f>K84+K85</f>
+        <f>K94-K95</f>
         <v/>
       </c>
       <c r="L96" s="16">
-        <f>L84+L85</f>
+        <f>L94-L95</f>
         <v/>
       </c>
       <c r="M96" s="16">
-        <f>M84+M85</f>
+        <f>M94-M95</f>
         <v/>
       </c>
       <c r="N96" s="16">
-        <f>N84+N85</f>
+        <f>N94-N95</f>
         <v/>
       </c>
     </row>
@@ -5887,16 +5879,46 @@
       <c r="B97" s="4" t="n"/>
       <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="4" t="n"/>
-      <c r="L97" s="4" t="n"/>
-      <c r="M97" s="4" t="n"/>
-      <c r="N97" s="4" t="n"/>
+      <c r="E97" s="4">
+        <f>E95+E96</f>
+        <v/>
+      </c>
+      <c r="F97" s="4">
+        <f>F95+F96</f>
+        <v/>
+      </c>
+      <c r="G97" s="4">
+        <f>G95+G96</f>
+        <v/>
+      </c>
+      <c r="H97" s="4">
+        <f>H95+H96</f>
+        <v/>
+      </c>
+      <c r="I97" s="4">
+        <f>I95+I96</f>
+        <v/>
+      </c>
+      <c r="J97" s="4">
+        <f>J95+J96</f>
+        <v/>
+      </c>
+      <c r="K97" s="4">
+        <f>K95+K96</f>
+        <v/>
+      </c>
+      <c r="L97" s="4">
+        <f>L95+L96</f>
+        <v/>
+      </c>
+      <c r="M97" s="4">
+        <f>M95+M96</f>
+        <v/>
+      </c>
+      <c r="N97" s="4">
+        <f>N95+N96</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -6025,47 +6047,88 @@
         </is>
       </c>
       <c r="E100" s="7">
-        <f>IF(E89="PASS",MAX(0,E88),0)</f>
+        <f>E77-E82-E87-E96</f>
         <v/>
       </c>
       <c r="F100" s="7">
-        <f>IF(F89="PASS",MAX(0,F88),0)</f>
+        <f>F77-F82-F87-F96</f>
         <v/>
       </c>
       <c r="G100" s="7">
-        <f>IF(G89="PASS",MAX(0,G88),0)</f>
+        <f>G77-G82-G87-G96</f>
         <v/>
       </c>
       <c r="H100" s="7">
-        <f>IF(H89="PASS",MAX(0,H88),0)</f>
+        <f>H77-H82-H87-H96</f>
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IF(I89="PASS",MAX(0,I88),0)</f>
+        <f>I77-I82-I87-I96</f>
         <v/>
       </c>
       <c r="J100" s="7">
-        <f>IF(J89="PASS",MAX(0,J88),0)</f>
+        <f>J77-J82-J87-J96</f>
         <v/>
       </c>
       <c r="K100" s="7">
-        <f>IF(K89="PASS",MAX(0,K88),0)</f>
+        <f>K77-K82-K87-K96</f>
         <v/>
       </c>
       <c r="L100" s="7">
-        <f>IF(L89="PASS",MAX(0,L88),0)</f>
+        <f>L77-L82-L87-L96</f>
         <v/>
       </c>
       <c r="M100" s="7">
-        <f>IF(M89="PASS",MAX(0,M88),0)</f>
+        <f>M77-M82-M87-M96</f>
         <v/>
       </c>
       <c r="N100" s="7">
-        <f>IF(N89="PASS",MAX(0,N88),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101"/>
+        <f>N77-N82-N87-N96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="E101">
+        <f>IF(E89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>IF(F89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G101">
+        <f>IF(G89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H101">
+        <f>IF(H89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I101">
+        <f>IF(I89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J101">
+        <f>IF(J89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K101">
+        <f>IF(K89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L101">
+        <f>IF(L89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M101">
+        <f>IF(M89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N101">
+        <f>IF(N89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
@@ -6075,16 +6138,46 @@
       <c r="B102" s="4" t="n"/>
       <c r="C102" s="4" t="n"/>
       <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="4" t="n"/>
-      <c r="N102" s="4" t="n"/>
+      <c r="E102" s="4">
+        <f>IF(E101="PASS",MAX(0,E100),0)</f>
+        <v/>
+      </c>
+      <c r="F102" s="4">
+        <f>IF(F101="PASS",MAX(0,F100),0)</f>
+        <v/>
+      </c>
+      <c r="G102" s="4">
+        <f>IF(G101="PASS",MAX(0,G100),0)</f>
+        <v/>
+      </c>
+      <c r="H102" s="4">
+        <f>IF(H101="PASS",MAX(0,H100),0)</f>
+        <v/>
+      </c>
+      <c r="I102" s="4">
+        <f>IF(I101="PASS",MAX(0,I100),0)</f>
+        <v/>
+      </c>
+      <c r="J102" s="4">
+        <f>IF(J101="PASS",MAX(0,J100),0)</f>
+        <v/>
+      </c>
+      <c r="K102" s="4">
+        <f>IF(K101="PASS",MAX(0,K100),0)</f>
+        <v/>
+      </c>
+      <c r="L102" s="4">
+        <f>IF(L101="PASS",MAX(0,L100),0)</f>
+        <v/>
+      </c>
+      <c r="M102" s="4">
+        <f>IF(M101="PASS",MAX(0,M100),0)</f>
+        <v/>
+      </c>
+      <c r="N102" s="4">
+        <f>IF(N101="PASS",MAX(0,N100),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="21" t="inlineStr">
@@ -6142,7 +6235,7 @@
       </c>
       <c r="C106" s="6" t="inlineStr"/>
       <c r="D106" s="16">
-        <f>D83</f>
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
@@ -6159,11 +6252,16 @@
       </c>
       <c r="C107" s="6" t="inlineStr"/>
       <c r="D107" s="7">
-        <f>D94+D95+D96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108"/>
+        <f>$D$27*$D$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="D108">
+        <f>E94</f>
+        <v/>
+      </c>
+    </row>
     <row r="109">
       <c r="A109" s="21" t="inlineStr">
         <is>
@@ -6172,6 +6270,10 @@
       </c>
       <c r="B109" s="6" t="inlineStr"/>
       <c r="C109" s="6" t="inlineStr"/>
+      <c r="D109">
+        <f>D106+D107+D108</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -6224,7 +6326,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="7">
-        <f>D100+D101</f>
+        <f>$D$27*$D$47</f>
         <v/>
       </c>
     </row>
@@ -6237,11 +6339,16 @@
       <c r="B113" s="6" t="inlineStr"/>
       <c r="C113" s="6" t="inlineStr"/>
       <c r="D113" s="10">
-        <f>IF(ABS(D97-D102)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114"/>
+        <f>D109-D112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="D114">
+        <f>D112+D113</f>
+        <v/>
+      </c>
+    </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
@@ -6278,6 +6385,10 @@
           <t>Exit Multiple × Exit Yr EBITDA</t>
         </is>
       </c>
+      <c r="D116">
+        <f>IF(ABS(D109-D114)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
       <c r="K116" s="16">
         <f>$D$19*K62</f>
         <v/>
@@ -6341,12 +6452,21 @@
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
+      <c r="D119">
+        <f>K72</f>
+        <v/>
+      </c>
       <c r="K119" s="7">
         <f>K106-K107+K108</f>
         <v/>
       </c>
     </row>
-    <row r="120"/>
+    <row r="120">
+      <c r="D120">
+        <f>D119*$D$29</f>
+        <v/>
+      </c>
+    </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
@@ -6355,7 +6475,10 @@
       </c>
       <c r="B121" s="4" t="n"/>
       <c r="C121" s="4" t="n"/>
-      <c r="D121" s="4" t="n"/>
+      <c r="D121" s="4">
+        <f>K88</f>
+        <v/>
+      </c>
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="4" t="n"/>
@@ -6380,7 +6503,7 @@
       </c>
       <c r="C122" s="6" t="inlineStr"/>
       <c r="D122" s="16">
-        <f>-D101</f>
+        <f>K97</f>
         <v/>
       </c>
       <c r="E122" s="16">
@@ -6441,7 +6564,7 @@
         </is>
       </c>
       <c r="D123" s="23">
-        <f>IRR(D112:K112)</f>
+        <f>D120-D121+D122</f>
         <v/>
       </c>
     </row>
@@ -6466,7 +6589,6 @@
         <v/>
       </c>
     </row>
-    <row r="125"/>
     <row r="126">
       <c r="A126" s="21" t="inlineStr">
         <is>
@@ -6475,6 +6597,47 @@
       </c>
       <c r="B126" s="6" t="inlineStr"/>
       <c r="C126" s="6" t="inlineStr"/>
+      <c r="D126">
+        <f>-D113</f>
+        <v/>
+      </c>
+      <c r="E126">
+        <f>E102</f>
+        <v/>
+      </c>
+      <c r="F126">
+        <f>F102</f>
+        <v/>
+      </c>
+      <c r="G126">
+        <f>G102</f>
+        <v/>
+      </c>
+      <c r="H126">
+        <f>H102</f>
+        <v/>
+      </c>
+      <c r="I126">
+        <f>I102</f>
+        <v/>
+      </c>
+      <c r="J126">
+        <f>J102</f>
+        <v/>
+      </c>
+      <c r="K126">
+        <f>K102+D123</f>
+        <v/>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -6488,8 +6651,8 @@
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr"/>
-      <c r="D127" s="16">
-        <f>-$D$17-D95</f>
+      <c r="D127" s="23">
+        <f>IRR(D126:N126)</f>
         <v/>
       </c>
       <c r="E127" s="16">
@@ -6549,8 +6712,57 @@
           <t>IRR of Equity CFs</t>
         </is>
       </c>
-      <c r="D128" s="23">
-        <f>IRR(D117:K117)</f>
+      <c r="D128" s="22">
+        <f>(SUM(E126:K126))/-D126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="D131">
+        <f>-$D$27-D107</f>
+        <v/>
+      </c>
+      <c r="E131">
+        <f>E77</f>
+        <v/>
+      </c>
+      <c r="F131">
+        <f>F77</f>
+        <v/>
+      </c>
+      <c r="G131">
+        <f>G77</f>
+        <v/>
+      </c>
+      <c r="H131">
+        <f>H77</f>
+        <v/>
+      </c>
+      <c r="I131">
+        <f>I77</f>
+        <v/>
+      </c>
+      <c r="J131">
+        <f>J77</f>
+        <v/>
+      </c>
+      <c r="K131">
+        <f>K77+D120</f>
+        <v/>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="D132" s="52">
+        <f>IRR(D131:N131)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -4771,6 +4771,7 @@
         <v/>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -4808,43 +4809,43 @@
         </is>
       </c>
       <c r="E75" s="16">
-        <f>MAX(0,E72-$D$61)*$D$55</f>
+        <f>E72-$D$61</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>MAX(0,F72-$D$61)*$D$55</f>
+        <f>F72-$D$61</f>
         <v/>
       </c>
       <c r="G75" s="16">
-        <f>MAX(0,G72-$D$61)*$D$55</f>
+        <f>G72-$D$61</f>
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>MAX(0,H72-$D$61)*$D$55</f>
+        <f>H72-$D$61</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>MAX(0,I72-$D$61)*$D$55</f>
+        <f>I72-$D$61</f>
         <v/>
       </c>
       <c r="J75" s="16">
-        <f>MAX(0,J72-$D$61)*$D$55</f>
+        <f>J72-$D$61</f>
         <v/>
       </c>
       <c r="K75" s="16">
-        <f>MAX(0,K72-$D$61)*$D$55</f>
+        <f>K72-$D$61</f>
         <v/>
       </c>
       <c r="L75" s="16">
-        <f>MAX(0,L72-$D$61)*$D$55</f>
+        <f>L72-$D$61</f>
         <v/>
       </c>
       <c r="M75" s="16">
-        <f>MAX(0,M72-$D$61)*$D$55</f>
+        <f>M72-$D$61</f>
         <v/>
       </c>
       <c r="N75" s="16">
-        <f>MAX(0,N72-$D$61)*$D$55</f>
+        <f>N72-$D$61</f>
         <v/>
       </c>
     </row>
@@ -4865,43 +4866,43 @@
         </is>
       </c>
       <c r="E76" s="16">
-        <f>IF(1&lt;=5,$D$44,0)</f>
+        <f>MAX(0,E75)*$D$55</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>IF(2&lt;=5,$D$44,0)</f>
+        <f>MAX(0,F75)*$D$55</f>
         <v/>
       </c>
       <c r="G76" s="16">
-        <f>IF(3&lt;=5,$D$44,0)</f>
+        <f>MAX(0,G75)*$D$55</f>
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>IF(4&lt;=5,$D$44,0)</f>
+        <f>MAX(0,H75)*$D$55</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>IF(5&lt;=5,$D$44,0)</f>
+        <f>MAX(0,I75)*$D$55</f>
         <v/>
       </c>
       <c r="J76" s="16">
-        <f>IF(6&lt;=5,$D$44,0)</f>
+        <f>MAX(0,J75)*$D$55</f>
         <v/>
       </c>
       <c r="K76" s="16">
-        <f>IF(7&lt;=5,$D$44,0)</f>
+        <f>MAX(0,K75)*$D$55</f>
         <v/>
       </c>
       <c r="L76" s="16">
-        <f>IF(8&lt;=5,$D$44,0)</f>
+        <f>MAX(0,L75)*$D$55</f>
         <v/>
       </c>
       <c r="M76" s="16">
-        <f>IF(9&lt;=5,$D$44,0)</f>
+        <f>MAX(0,M75)*$D$55</f>
         <v/>
       </c>
       <c r="N76" s="16">
-        <f>IF(10&lt;=5,$D$44,0)</f>
+        <f>MAX(0,N75)*$D$55</f>
         <v/>
       </c>
     </row>
@@ -4922,43 +4923,43 @@
         </is>
       </c>
       <c r="E77" s="7">
-        <f>E72-E75-E76</f>
+        <f>IF(1&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="F77" s="7">
-        <f>F72-F75-F76</f>
+        <f>IF(2&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="G77" s="7">
-        <f>G72-G75-G76</f>
+        <f>IF(3&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="H77" s="7">
-        <f>H72-H75-H76</f>
+        <f>IF(4&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>I72-I75-I76</f>
+        <f>IF(5&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="J77" s="7">
-        <f>J72-J75-J76</f>
+        <f>IF(6&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="K77" s="7">
-        <f>K72-K75-K76</f>
+        <f>IF(7&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="L77" s="7">
-        <f>L72-L75-L76</f>
+        <f>IF(8&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="M77" s="7">
-        <f>M72-M75-M76</f>
+        <f>IF(9&lt;=5,$D$44,0)</f>
         <v/>
       </c>
       <c r="N77" s="7">
-        <f>N72-N75-N76</f>
+        <f>IF(10&lt;=5,$D$44,0)</f>
         <v/>
       </c>
     </row>
@@ -4979,46 +4980,47 @@
         </is>
       </c>
       <c r="E78" s="7">
-        <f>E62-E66-E67</f>
+        <f>E72-E76-E77</f>
         <v/>
       </c>
       <c r="F78" s="7">
-        <f>F62-F66-F67</f>
+        <f>F72-F76-F77</f>
         <v/>
       </c>
       <c r="G78" s="7">
-        <f>G62-G66-G67</f>
+        <f>G72-G76-G77</f>
         <v/>
       </c>
       <c r="H78" s="7">
-        <f>H62-H66-H67</f>
+        <f>H72-H76-H77</f>
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>I62-I66-I67</f>
+        <f>I72-I76-I77</f>
         <v/>
       </c>
       <c r="J78" s="7">
-        <f>J62-J66-J67</f>
+        <f>J72-J76-J77</f>
         <v/>
       </c>
       <c r="K78" s="7">
-        <f>K62-K66-K67</f>
+        <f>K72-K76-K77</f>
         <v/>
       </c>
       <c r="L78" s="7">
-        <f>L62-L66-L67</f>
+        <f>L72-L76-L77</f>
         <v/>
       </c>
       <c r="M78" s="7">
-        <f>M62-M66-M67</f>
+        <f>M72-M76-M77</f>
         <v/>
       </c>
       <c r="N78" s="7">
-        <f>N62-N66-N67</f>
-        <v/>
-      </c>
-    </row>
+        <f>N72-N76-N77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -6201,7 +6203,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr"/>
       <c r="D104" s="16">
-        <f>$D$17</f>
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
@@ -6218,7 +6220,7 @@
       </c>
       <c r="C105" s="6" t="inlineStr"/>
       <c r="D105" s="16">
-        <f>$D$17*$D$18</f>
+        <f>$D$27*$D$28</f>
         <v/>
       </c>
     </row>
@@ -6235,7 +6237,7 @@
       </c>
       <c r="C106" s="6" t="inlineStr"/>
       <c r="D106" s="16">
-        <f>$D$27</f>
+        <f>E94</f>
         <v/>
       </c>
     </row>
@@ -6252,7 +6254,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr"/>
       <c r="D107" s="7">
-        <f>$D$27*$D$28</f>
+        <f>D104+D105+D106</f>
         <v/>
       </c>
     </row>
@@ -6288,7 +6290,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr"/>
       <c r="D110" s="16">
-        <f>$D$50</f>
+        <f>$D$27*$D$47</f>
         <v/>
       </c>
     </row>
@@ -6309,7 +6311,7 @@
         </is>
       </c>
       <c r="D111" s="16">
-        <f>D97-D100</f>
+        <f>D107-D110</f>
         <v/>
       </c>
     </row>
@@ -6326,7 +6328,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="7">
-        <f>$D$27*$D$47</f>
+        <f>D110+D111</f>
         <v/>
       </c>
     </row>
@@ -6339,7 +6341,7 @@
       <c r="B113" s="6" t="inlineStr"/>
       <c r="C113" s="6" t="inlineStr"/>
       <c r="D113" s="10">
-        <f>D109-D112</f>
+        <f>IF(ABS(D107-D112)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -6386,7 +6388,7 @@
         </is>
       </c>
       <c r="D116">
-        <f>IF(ABS(D109-D114)&lt;0.01,"PASS","FAIL")</f>
+        <f>K72*$D$29</f>
         <v/>
       </c>
       <c r="K116" s="16">
@@ -6410,6 +6412,10 @@
           <t>Ending Bal at Exit</t>
         </is>
       </c>
+      <c r="D117">
+        <f>K88</f>
+        <v/>
+      </c>
       <c r="K117" s="16">
         <f>K78</f>
         <v/>
@@ -6431,6 +6437,10 @@
           <t>DSRA Ending at Exit</t>
         </is>
       </c>
+      <c r="D118">
+        <f>K97</f>
+        <v/>
+      </c>
       <c r="K118" s="16">
         <f>K86</f>
         <v/>
@@ -6453,7 +6463,7 @@
         </is>
       </c>
       <c r="D119">
-        <f>K72</f>
+        <f>D116-D117+D118</f>
         <v/>
       </c>
       <c r="K119" s="7">
@@ -6503,48 +6513,45 @@
       </c>
       <c r="C122" s="6" t="inlineStr"/>
       <c r="D122" s="16">
-        <f>K97</f>
+        <f>-D111</f>
         <v/>
       </c>
       <c r="E122" s="16">
-        <f>E90</f>
+        <f>E100</f>
         <v/>
       </c>
       <c r="F122" s="16">
-        <f>F90</f>
+        <f>F100</f>
         <v/>
       </c>
       <c r="G122" s="16">
-        <f>G90</f>
+        <f>G100</f>
         <v/>
       </c>
       <c r="H122" s="16">
-        <f>H90</f>
+        <f>H100</f>
         <v/>
       </c>
       <c r="I122" s="16">
-        <f>I90</f>
+        <f>I100</f>
         <v/>
       </c>
       <c r="J122" s="16">
-        <f>J90</f>
+        <f>J100</f>
         <v/>
       </c>
       <c r="K122" s="16">
-        <f>K90+K109</f>
-        <v/>
-      </c>
-      <c r="L122" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M122" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N122" s="16">
-        <f>0</f>
-        <v/>
+        <f>K100+D119</f>
+        <v/>
+      </c>
+      <c r="L122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6564,7 +6571,7 @@
         </is>
       </c>
       <c r="D123" s="23">
-        <f>D120-D121+D122</f>
+        <f>IRR(D122:N122)</f>
         <v/>
       </c>
     </row>
@@ -6585,7 +6592,7 @@
         </is>
       </c>
       <c r="D124" s="22">
-        <f>SUMIF(D112:K112,"&gt;0")/ABS(D112)</f>
+        <f>(SUM(E122:K122))/-D122</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -4771,7 +4771,6 @@
         <v/>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -5020,7 +5019,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -6599,41 +6597,41 @@
     <row r="126">
       <c r="A126" s="21" t="inlineStr">
         <is>
-          <t>Unlevered Returns (for reference)</t>
+          <t>Unlevered Cash Flow</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr"/>
       <c r="C126" s="6" t="inlineStr"/>
       <c r="D126">
-        <f>-D113</f>
+        <f>-D104</f>
         <v/>
       </c>
       <c r="E126">
-        <f>E102</f>
+        <f>E78</f>
         <v/>
       </c>
       <c r="F126">
-        <f>F102</f>
+        <f>F78</f>
         <v/>
       </c>
       <c r="G126">
-        <f>G102</f>
+        <f>G78</f>
         <v/>
       </c>
       <c r="H126">
-        <f>H102</f>
+        <f>H78</f>
         <v/>
       </c>
       <c r="I126">
-        <f>I102</f>
+        <f>I78</f>
         <v/>
       </c>
       <c r="J126">
-        <f>J102</f>
+        <f>J78</f>
         <v/>
       </c>
       <c r="K126">
-        <f>K102+D123</f>
+        <f>K78+D121</f>
         <v/>
       </c>
       <c r="L126" t="n">
@@ -6649,7 +6647,7 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Unlevered Cash Flow</t>
+          <t>Unlevered IRR</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -6706,7 +6704,7 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Unlevered IRR</t>
+          <t>Unlevered MOIC</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -3765,7 +3765,7 @@
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="10">
-        <f>IF(I78&lt;1,"PASS","FAIL")</f>
+        <f>IF(I88&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -3751,10 +3751,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="10">
-        <f>D103</f>
-        <v/>
-      </c>
+      <c r="D21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3782,7 +3779,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(MINIFS(E89:I89,E89:I89,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_5_Midstream.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -235,6 +235,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3550,10 +3551,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="53">
+        <f>IF(COUNTIF(E89:I89,"&gt;0")&gt;0,MINIFS(E89:I89,E89:I89,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="45" t="inlineStr">
@@ -3779,7 +3795,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(MINIFS(E89:I89,E89:I89,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
